--- a/data/spss_svy_metadata.xlsx
+++ b/data/spss_svy_metadata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://forsmarshgroup-my.sharepoint.com/personal/rpowell_forsmarsh_com/Documents/Documents/GitHub/daro-training/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://forsmarshgroup-my.sharepoint.com/personal/rpowell_forsmarsh_com/Documents/Documents/GitHub/daro-training-site/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="334" documentId="8_{1F86A6CC-B199-4477-854B-C39149FB1DC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E900031-6885-4BCF-8D14-03CADCFFE241}"/>
+  <xr:revisionPtr revIDLastSave="359" documentId="8_{1F86A6CC-B199-4477-854B-C39149FB1DC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{446BB022-3F60-4CD2-BDE0-2A5646C2E603}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{4BB05424-074A-4AE7-934F-662DB208E1AC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{4BB05424-074A-4AE7-934F-662DB208E1AC}"/>
   </bookViews>
   <sheets>
     <sheet name="varnames_labels" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="326">
   <si>
     <t>CaseId</t>
   </si>
@@ -258,75 +258,21 @@
     <t>Device Browser Version</t>
   </si>
   <si>
-    <t>PRIVACY ACT STATEMENTIn accordance with the Privacy Act of 1974 (Public Law 93-579), this notice informs you of the purpose of the survey and how the findings will be used. Please read it carefully.AUTHORITY: 10 U.S.C. 503, 2358PRINCIPAL PURPOSE: Informat</t>
-  </si>
-  <si>
     <t>What is your age?</t>
   </si>
   <si>
-    <t>SURVEY CONTROL NUMBER: XXXX-XXX-XX-XXXAGENCY IDENTIFIER: AEMOExpiration Date: XX/XX/XXIf you are the parent or legal guardian of a child who may take part in this study, when “you” appears in this form, it refers to your child.If you are a minor, your</t>
-  </si>
-  <si>
-    <t>For parents/legal guardians of a minor: Do you provide consent for your child to participate in this study?</t>
-  </si>
-  <si>
-    <t>Have you ever been in the Military, are you in a college Reserve Officers’ Training Corps (ROTC) program or one of the Service academies, or have you been accepted to and are waiting to begin any of these programs?</t>
-  </si>
-  <si>
-    <t>In which branch did you serve?</t>
-  </si>
-  <si>
-    <t>Are you a parent of a 14- to 21-year-old?</t>
-  </si>
-  <si>
-    <t>Do you mentor or work with 14- to 21-year-olds for 10 or more hours each week?</t>
-  </si>
-  <si>
-    <t>Q5: Sample Assignment - to be hidden</t>
-  </si>
-  <si>
-    <t>What is your sex? var utag_data = { tealium_event : \\, // Identifies the unique names of tracked events. tealium_visitor_id : \\, // page_name : \\, // The user-friendly name of the page ddb_useragent : \\, // TeamDDB User Agent (Device Identifier)</t>
-  </si>
-  <si>
     <t>gender</t>
   </si>
   <si>
     <t>Are you of Hispanic, Latino, or Spanish origin?</t>
   </si>
   <si>
-    <t>What is your race? Please select one or more races to indicate the race or races that you consider yourself to be. 1 = White</t>
-  </si>
-  <si>
-    <t>What is your race? Please select one or more races to indicate the race or races that you consider yourself to be. 2 = Black or African American</t>
-  </si>
-  <si>
-    <t>What is your race? Please select one or more races to indicate the race or races that you consider yourself to be. 3 = American Indian or Alaska Native</t>
-  </si>
-  <si>
-    <t>What is your race? Please select one or more races to indicate the race or races that you consider yourself to be. 4 = Asian (e.g., Asian Indian, Chinese, Filipino, Japanese, Korean, Vietnamese)</t>
-  </si>
-  <si>
-    <t>What is your race? Please select one or more races to indicate the race or races that you consider yourself to be. 5 = Native Hawaiian or other Pacific Islander (e.g., Native Hawaiian, Samoan, Chamorro, Tongan, Fijian, Marshallese)</t>
-  </si>
-  <si>
-    <t>What is your race? Please select one or more races to indicate the race or races that you consider yourself to be. 6 = Some other race</t>
-  </si>
-  <si>
-    <t>to be hidden</t>
-  </si>
-  <si>
     <t>What is your ZIP code? Please enter only the first five digits.</t>
   </si>
   <si>
     <t>What state do you live in?</t>
   </si>
   <si>
-    <t>state region</t>
-  </si>
-  <si>
-    <t>In the next few years, how likely is it that you will be serving in the Army?</t>
-  </si>
-  <si>
     <t>What is the highest level of school you have completed?</t>
   </si>
   <si>
@@ -366,15 +312,6 @@
     <t>What is your current education status?</t>
   </si>
   <si>
-    <t>Thinking ahead to after you finish high school, do you plan to go directly to either a two-year or a four-year college that same calendar year as your graduation?</t>
-  </si>
-  <si>
-    <t>What was the total combined income of all of the members of your household in 2024? Please give your best estimate.</t>
-  </si>
-  <si>
-    <t>Q36 - to be hidden</t>
-  </si>
-  <si>
     <t>new_label</t>
   </si>
   <si>
@@ -1024,6 +961,60 @@
   </si>
   <si>
     <t>Answered</t>
+  </si>
+  <si>
+    <t>PRIVACY ACT STATEMENT</t>
+  </si>
+  <si>
+    <t>Consent</t>
+  </si>
+  <si>
+    <t>Parent/legal guardian consent</t>
+  </si>
+  <si>
+    <t>Past Military Question</t>
+  </si>
+  <si>
+    <t>Branch</t>
+  </si>
+  <si>
+    <t>Are you a parent?</t>
+  </si>
+  <si>
+    <t>Do you mentor kids?</t>
+  </si>
+  <si>
+    <t>Hidden: Segment</t>
+  </si>
+  <si>
+    <t>What is your sex?</t>
+  </si>
+  <si>
+    <t>What is your race? Please select one or more races. 1 = White</t>
+  </si>
+  <si>
+    <t>What is your race? Please select one or more races. 2 = Black or African American</t>
+  </si>
+  <si>
+    <t>What is your race? Please select one or more races. 3 = American Indian or Alaska Native</t>
+  </si>
+  <si>
+    <t>What is your race? Please select one or more races. 6 = Some other race</t>
+  </si>
+  <si>
+    <t>Army likelihood</t>
+  </si>
+  <si>
+    <t>College plans</t>
+  </si>
+  <si>
+    <t>Household income</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What is your race? Please select one or more races. 5 = Native Hawaiian or other Pacific Islander </t>
+  </si>
+  <si>
+    <t xml:space="preserve">What is your race? Please select one or more races. 4 = Asian </t>
   </si>
 </sst>
 </file>
@@ -1064,12 +1055,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1407,6 +1397,8 @@
   <dimension ref="A1:D60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="233.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1418,10 +1410,10 @@
         <v>59</v>
       </c>
       <c r="C1" t="s">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="D1" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -1625,13 +1617,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>73</v>
+        <v>308</v>
       </c>
       <c r="C16" t="s">
         <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1639,13 +1631,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C17" t="s">
         <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>116</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1659,7 +1651,7 @@
         <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1667,13 +1659,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>309</v>
       </c>
       <c r="C19" t="s">
         <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>122</v>
+        <v>101</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1681,13 +1673,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>76</v>
+        <v>310</v>
       </c>
       <c r="C20" t="s">
         <v>19</v>
       </c>
       <c r="D20" t="s">
-        <v>123</v>
+        <v>102</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1695,13 +1687,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>77</v>
+        <v>311</v>
       </c>
       <c r="C21" t="s">
         <v>20</v>
       </c>
       <c r="D21" t="s">
-        <v>124</v>
+        <v>103</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1709,13 +1701,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>78</v>
+        <v>312</v>
       </c>
       <c r="C22" t="s">
         <v>21</v>
       </c>
       <c r="D22" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1723,13 +1715,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>79</v>
+        <v>313</v>
       </c>
       <c r="C23" t="s">
         <v>22</v>
       </c>
       <c r="D23" t="s">
-        <v>126</v>
+        <v>105</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1737,13 +1729,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>80</v>
+        <v>314</v>
       </c>
       <c r="C24" t="s">
         <v>23</v>
       </c>
       <c r="D24" t="s">
-        <v>128</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1751,13 +1743,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>81</v>
+        <v>315</v>
       </c>
       <c r="C25" t="s">
         <v>24</v>
       </c>
       <c r="D25" t="s">
-        <v>129</v>
+        <v>108</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1765,13 +1757,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>82</v>
+        <v>316</v>
       </c>
       <c r="C26" t="s">
         <v>25</v>
       </c>
       <c r="D26" t="s">
-        <v>127</v>
+        <v>106</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1779,13 +1771,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="C27" t="s">
         <v>26</v>
       </c>
       <c r="D27" t="s">
-        <v>119</v>
+        <v>98</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1793,13 +1785,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="C28" t="s">
         <v>27</v>
       </c>
       <c r="D28" t="s">
-        <v>130</v>
+        <v>109</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1807,13 +1799,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>85</v>
+        <v>317</v>
       </c>
       <c r="C29" t="s">
-        <v>158</v>
+        <v>137</v>
       </c>
       <c r="D29" t="s">
-        <v>131</v>
+        <v>110</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1821,13 +1813,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>86</v>
+        <v>318</v>
       </c>
       <c r="C30" t="s">
-        <v>159</v>
+        <v>138</v>
       </c>
       <c r="D30" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1835,13 +1827,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>87</v>
+        <v>319</v>
       </c>
       <c r="C31" t="s">
-        <v>160</v>
+        <v>139</v>
       </c>
       <c r="D31" t="s">
-        <v>133</v>
+        <v>112</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1849,13 +1841,13 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>88</v>
+        <v>325</v>
       </c>
       <c r="C32" t="s">
-        <v>161</v>
+        <v>140</v>
       </c>
       <c r="D32" t="s">
-        <v>134</v>
+        <v>113</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1863,13 +1855,13 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>89</v>
+        <v>324</v>
       </c>
       <c r="C33" t="s">
-        <v>162</v>
+        <v>141</v>
       </c>
       <c r="D33" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1877,13 +1869,13 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>90</v>
+        <v>320</v>
       </c>
       <c r="C34" t="s">
-        <v>163</v>
+        <v>142</v>
       </c>
       <c r="D34" t="s">
-        <v>136</v>
+        <v>115</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1894,24 +1886,21 @@
         <v>1</v>
       </c>
       <c r="C35" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="D35" t="s">
-        <v>137</v>
+        <v>116</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>35</v>
       </c>
-      <c r="B36" t="s">
-        <v>91</v>
-      </c>
       <c r="C36" t="s">
         <v>35</v>
       </c>
       <c r="D36" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1919,13 +1908,13 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="C37" t="s">
         <v>36</v>
       </c>
       <c r="D37" t="s">
-        <v>138</v>
+        <v>117</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1933,27 +1922,24 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="C38" t="s">
         <v>37</v>
       </c>
       <c r="D38" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>38</v>
       </c>
-      <c r="B39" t="s">
-        <v>94</v>
-      </c>
       <c r="C39" t="s">
         <v>38</v>
       </c>
       <c r="D39" t="s">
-        <v>117</v>
+        <v>96</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1961,13 +1947,13 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>95</v>
+        <v>321</v>
       </c>
       <c r="C40" t="s">
         <v>39</v>
       </c>
       <c r="D40" t="s">
-        <v>140</v>
+        <v>119</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1981,7 +1967,7 @@
         <v>40</v>
       </c>
       <c r="D41" t="s">
-        <v>121</v>
+        <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1989,13 +1975,13 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="C42" t="s">
         <v>41</v>
       </c>
       <c r="D42" t="s">
-        <v>141</v>
+        <v>120</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -2003,13 +1989,13 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="C43" t="s">
         <v>42</v>
       </c>
       <c r="D43" t="s">
-        <v>142</v>
+        <v>121</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -2017,13 +2003,13 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="C44" t="s">
-        <v>164</v>
+        <v>143</v>
       </c>
       <c r="D44" t="s">
-        <v>143</v>
+        <v>122</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -2031,13 +2017,13 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="C45" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="D45" t="s">
-        <v>147</v>
+        <v>126</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -2045,13 +2031,13 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="C46" t="s">
-        <v>166</v>
+        <v>145</v>
       </c>
       <c r="D46" t="s">
-        <v>148</v>
+        <v>127</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -2059,13 +2045,13 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="C47" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="D47" t="s">
-        <v>149</v>
+        <v>128</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -2073,13 +2059,13 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="C48" t="s">
-        <v>168</v>
+        <v>147</v>
       </c>
       <c r="D48" t="s">
-        <v>150</v>
+        <v>129</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -2087,13 +2073,13 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="C49" t="s">
-        <v>169</v>
+        <v>148</v>
       </c>
       <c r="D49" t="s">
-        <v>151</v>
+        <v>130</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -2101,13 +2087,13 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="C50" t="s">
-        <v>170</v>
+        <v>149</v>
       </c>
       <c r="D50" t="s">
-        <v>152</v>
+        <v>131</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -2115,13 +2101,13 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="C51" t="s">
-        <v>171</v>
+        <v>150</v>
       </c>
       <c r="D51" t="s">
-        <v>153</v>
+        <v>132</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -2129,13 +2115,13 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="C52" t="s">
-        <v>172</v>
+        <v>151</v>
       </c>
       <c r="D52" t="s">
-        <v>154</v>
+        <v>133</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -2143,13 +2129,13 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="C53" t="s">
-        <v>173</v>
+        <v>152</v>
       </c>
       <c r="D53" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -2160,10 +2146,10 @@
         <v>1</v>
       </c>
       <c r="C54" t="s">
-        <v>175</v>
+        <v>154</v>
       </c>
       <c r="D54" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -2171,13 +2157,13 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="C55" t="s">
         <v>54</v>
       </c>
       <c r="D55" t="s">
-        <v>144</v>
+        <v>123</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -2185,13 +2171,13 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>109</v>
+        <v>322</v>
       </c>
       <c r="C56" t="s">
         <v>55</v>
       </c>
       <c r="D56" t="s">
-        <v>145</v>
+        <v>124</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -2199,27 +2185,24 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>110</v>
+        <v>323</v>
       </c>
       <c r="C57" t="s">
         <v>56</v>
       </c>
       <c r="D57" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>57</v>
       </c>
-      <c r="B58" t="s">
-        <v>111</v>
-      </c>
       <c r="C58" t="s">
         <v>57</v>
       </c>
       <c r="D58" t="s">
-        <v>293</v>
+        <v>272</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -2234,6 +2217,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2251,10 +2235,10 @@
         <v>58</v>
       </c>
       <c r="B1" t="s">
-        <v>178</v>
+        <v>157</v>
       </c>
       <c r="C1" t="s">
-        <v>179</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -2300,7 +2284,7 @@
         <v>0</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>180</v>
+        <v>159</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -2311,7 +2295,7 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -2322,7 +2306,7 @@
         <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>181</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -2333,7 +2317,7 @@
         <v>3</v>
       </c>
       <c r="C12" t="s">
-        <v>182</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -2344,7 +2328,7 @@
         <v>4</v>
       </c>
       <c r="C13" t="s">
-        <v>183</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -2355,7 +2339,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="s">
-        <v>184</v>
+        <v>163</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -2366,7 +2350,7 @@
         <v>6</v>
       </c>
       <c r="C15" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -2407,7 +2391,7 @@
         <v>1</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>186</v>
+        <v>165</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -2418,7 +2402,7 @@
         <v>2</v>
       </c>
       <c r="C23" t="s">
-        <v>187</v>
+        <v>166</v>
       </c>
       <c r="F23" s="1"/>
     </row>
@@ -2436,7 +2420,7 @@
         <v>1</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>188</v>
+        <v>167</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -2447,7 +2431,7 @@
         <v>2</v>
       </c>
       <c r="C26" t="s">
-        <v>189</v>
+        <v>168</v>
       </c>
       <c r="D26" s="1"/>
     </row>
@@ -2459,7 +2443,7 @@
         <v>3</v>
       </c>
       <c r="C27" t="s">
-        <v>190</v>
+        <v>169</v>
       </c>
       <c r="D27" s="1"/>
     </row>
@@ -2471,7 +2455,7 @@
         <v>4</v>
       </c>
       <c r="C28" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -2482,7 +2466,7 @@
         <v>5</v>
       </c>
       <c r="C29" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -2493,7 +2477,7 @@
         <v>6</v>
       </c>
       <c r="C30" t="s">
-        <v>192</v>
+        <v>171</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -2504,7 +2488,7 @@
         <v>7</v>
       </c>
       <c r="C31" t="s">
-        <v>193</v>
+        <v>172</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -2515,7 +2499,7 @@
         <v>0</v>
       </c>
       <c r="C32" t="s">
-        <v>201</v>
+        <v>180</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -2526,7 +2510,7 @@
         <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>202</v>
+        <v>181</v>
       </c>
       <c r="F33" s="1"/>
     </row>
@@ -2538,7 +2522,7 @@
         <v>2</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>176</v>
+        <v>155</v>
       </c>
       <c r="F34" s="1"/>
     </row>
@@ -2550,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>199</v>
+        <v>178</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -2561,7 +2545,7 @@
         <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="G36" s="1"/>
     </row>
@@ -2573,7 +2557,7 @@
         <v>0</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>195</v>
+        <v>174</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -2584,7 +2568,7 @@
         <v>1</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="G38" s="1"/>
     </row>
@@ -2596,7 +2580,7 @@
         <v>2</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>197</v>
+        <v>176</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -2607,7 +2591,7 @@
         <v>3</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>177</v>
+        <v>156</v>
       </c>
       <c r="G40" s="1"/>
     </row>
@@ -2619,7 +2603,7 @@
         <v>4</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>198</v>
+        <v>177</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -2630,7 +2614,7 @@
         <v>-99</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>203</v>
+        <v>182</v>
       </c>
       <c r="G42" s="1"/>
     </row>
@@ -2642,7 +2626,7 @@
         <v>1</v>
       </c>
       <c r="C43" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -2653,7 +2637,7 @@
         <v>2</v>
       </c>
       <c r="C44" t="s">
-        <v>204</v>
+        <v>183</v>
       </c>
       <c r="G44" s="1"/>
     </row>
@@ -2665,7 +2649,7 @@
         <v>3</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>205</v>
+        <v>184</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -2676,7 +2660,7 @@
         <v>4</v>
       </c>
       <c r="C46" t="s">
-        <v>206</v>
+        <v>185</v>
       </c>
       <c r="G46" s="1"/>
     </row>
@@ -2688,7 +2672,7 @@
         <v>5</v>
       </c>
       <c r="C47" t="s">
-        <v>207</v>
+        <v>186</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -2699,7 +2683,7 @@
         <v>6</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
       <c r="G48" s="1"/>
     </row>
@@ -2711,7 +2695,7 @@
         <v>7</v>
       </c>
       <c r="C49" t="s">
-        <v>209</v>
+        <v>188</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -2722,7 +2706,7 @@
         <v>8</v>
       </c>
       <c r="C50" t="s">
-        <v>210</v>
+        <v>189</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -2733,7 +2717,7 @@
         <v>9</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>211</v>
+        <v>190</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -2744,7 +2728,7 @@
         <v>10</v>
       </c>
       <c r="C52" t="s">
-        <v>212</v>
+        <v>191</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -2755,7 +2739,7 @@
         <v>11</v>
       </c>
       <c r="C53" t="s">
-        <v>213</v>
+        <v>192</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -2766,7 +2750,7 @@
         <v>0</v>
       </c>
       <c r="C54" t="s">
-        <v>214</v>
+        <v>193</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -2777,7 +2761,7 @@
         <v>1</v>
       </c>
       <c r="C55" t="s">
-        <v>215</v>
+        <v>194</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -2788,7 +2772,7 @@
         <v>0</v>
       </c>
       <c r="C56" t="s">
-        <v>214</v>
+        <v>193</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -2799,7 +2783,7 @@
         <v>1</v>
       </c>
       <c r="C57" t="s">
-        <v>215</v>
+        <v>194</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -2810,7 +2794,7 @@
         <v>1</v>
       </c>
       <c r="C58" t="s">
-        <v>216</v>
+        <v>195</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -2821,7 +2805,7 @@
         <v>2</v>
       </c>
       <c r="C59" t="s">
-        <v>217</v>
+        <v>196</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -2832,7 +2816,7 @@
         <v>3</v>
       </c>
       <c r="C60" t="s">
-        <v>218</v>
+        <v>197</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
@@ -2843,7 +2827,7 @@
         <v>1</v>
       </c>
       <c r="C61" t="s">
-        <v>219</v>
+        <v>198</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
@@ -2854,7 +2838,7 @@
         <v>2</v>
       </c>
       <c r="C62" t="s">
-        <v>220</v>
+        <v>199</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -2865,7 +2849,7 @@
         <v>3</v>
       </c>
       <c r="C63" t="s">
-        <v>221</v>
+        <v>200</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
@@ -2876,7 +2860,7 @@
         <v>1</v>
       </c>
       <c r="C64" t="s">
-        <v>219</v>
+        <v>198</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -2887,7 +2871,7 @@
         <v>2</v>
       </c>
       <c r="C65" t="s">
-        <v>222</v>
+        <v>201</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -2898,7 +2882,7 @@
         <v>0</v>
       </c>
       <c r="C66" t="s">
-        <v>214</v>
+        <v>193</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -2909,161 +2893,161 @@
         <v>1</v>
       </c>
       <c r="C67" t="s">
-        <v>215</v>
+        <v>194</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>158</v>
+        <v>137</v>
       </c>
       <c r="B68">
         <v>0</v>
       </c>
       <c r="C68" t="s">
-        <v>214</v>
+        <v>193</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>158</v>
+        <v>137</v>
       </c>
       <c r="B69">
         <v>1</v>
       </c>
       <c r="C69" t="s">
-        <v>215</v>
+        <v>194</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>159</v>
+        <v>138</v>
       </c>
       <c r="B70">
         <v>0</v>
       </c>
       <c r="C70" t="s">
-        <v>214</v>
+        <v>193</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>159</v>
+        <v>138</v>
       </c>
       <c r="B71">
         <v>1</v>
       </c>
       <c r="C71" t="s">
-        <v>215</v>
+        <v>194</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>160</v>
+        <v>139</v>
       </c>
       <c r="B72">
         <v>0</v>
       </c>
       <c r="C72" t="s">
-        <v>214</v>
+        <v>193</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>160</v>
+        <v>139</v>
       </c>
       <c r="B73">
         <v>1</v>
       </c>
       <c r="C73" t="s">
-        <v>215</v>
+        <v>194</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>161</v>
+        <v>140</v>
       </c>
       <c r="B74">
         <v>0</v>
       </c>
       <c r="C74" t="s">
-        <v>214</v>
+        <v>193</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>161</v>
+        <v>140</v>
       </c>
       <c r="B75">
         <v>1</v>
       </c>
       <c r="C75" t="s">
-        <v>215</v>
+        <v>194</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>162</v>
+        <v>141</v>
       </c>
       <c r="B76">
         <v>0</v>
       </c>
       <c r="C76" t="s">
-        <v>214</v>
+        <v>193</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>162</v>
+        <v>141</v>
       </c>
       <c r="B77">
         <v>1</v>
       </c>
       <c r="C77" t="s">
-        <v>215</v>
+        <v>194</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>163</v>
+        <v>142</v>
       </c>
       <c r="B78">
         <v>0</v>
       </c>
       <c r="C78" t="s">
-        <v>214</v>
+        <v>193</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>163</v>
+        <v>142</v>
       </c>
       <c r="B79">
         <v>1</v>
       </c>
       <c r="C79" t="s">
-        <v>215</v>
+        <v>194</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="B80">
         <v>0</v>
       </c>
       <c r="C80" t="s">
-        <v>328</v>
+        <v>307</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="B81">
         <v>1</v>
       </c>
       <c r="C81" t="s">
-        <v>203</v>
+        <v>182</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
@@ -3074,7 +3058,7 @@
         <v>1</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>223</v>
+        <v>202</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
@@ -3085,7 +3069,7 @@
         <v>2</v>
       </c>
       <c r="C83" t="s">
-        <v>224</v>
+        <v>203</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
@@ -3096,7 +3080,7 @@
         <v>3</v>
       </c>
       <c r="C84" t="s">
-        <v>225</v>
+        <v>204</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
@@ -3107,7 +3091,7 @@
         <v>4</v>
       </c>
       <c r="C85" t="s">
-        <v>226</v>
+        <v>205</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -3118,7 +3102,7 @@
         <v>5</v>
       </c>
       <c r="C86" t="s">
-        <v>227</v>
+        <v>206</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
@@ -3134,7 +3118,7 @@
         <v>1</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>228</v>
+        <v>207</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
@@ -3145,7 +3129,7 @@
         <v>2</v>
       </c>
       <c r="C89" t="s">
-        <v>229</v>
+        <v>208</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
@@ -3156,7 +3140,7 @@
         <v>3</v>
       </c>
       <c r="C90" t="s">
-        <v>230</v>
+        <v>209</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
@@ -3167,7 +3151,7 @@
         <v>4</v>
       </c>
       <c r="C91" t="s">
-        <v>231</v>
+        <v>210</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
@@ -3178,7 +3162,7 @@
         <v>5</v>
       </c>
       <c r="C92" t="s">
-        <v>232</v>
+        <v>211</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
@@ -3189,7 +3173,7 @@
         <v>6</v>
       </c>
       <c r="C93" t="s">
-        <v>233</v>
+        <v>212</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
@@ -3200,7 +3184,7 @@
         <v>7</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>234</v>
+        <v>213</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
@@ -3211,7 +3195,7 @@
         <v>8</v>
       </c>
       <c r="C95" t="s">
-        <v>235</v>
+        <v>214</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
@@ -3222,7 +3206,7 @@
         <v>9</v>
       </c>
       <c r="C96" t="s">
-        <v>236</v>
+        <v>215</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
@@ -3233,7 +3217,7 @@
         <v>10</v>
       </c>
       <c r="C97" t="s">
-        <v>237</v>
+        <v>216</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
@@ -3244,7 +3228,7 @@
         <v>11</v>
       </c>
       <c r="C98" t="s">
-        <v>238</v>
+        <v>217</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
@@ -3255,7 +3239,7 @@
         <v>12</v>
       </c>
       <c r="C99" t="s">
-        <v>239</v>
+        <v>218</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -3266,7 +3250,7 @@
         <v>13</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>240</v>
+        <v>219</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
@@ -3277,7 +3261,7 @@
         <v>14</v>
       </c>
       <c r="C101" t="s">
-        <v>241</v>
+        <v>220</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
@@ -3288,7 +3272,7 @@
         <v>15</v>
       </c>
       <c r="C102" t="s">
-        <v>242</v>
+        <v>221</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
@@ -3299,7 +3283,7 @@
         <v>16</v>
       </c>
       <c r="C103" t="s">
-        <v>243</v>
+        <v>222</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
@@ -3310,7 +3294,7 @@
         <v>17</v>
       </c>
       <c r="C104" t="s">
-        <v>244</v>
+        <v>223</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
@@ -3321,7 +3305,7 @@
         <v>18</v>
       </c>
       <c r="C105" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
@@ -3332,7 +3316,7 @@
         <v>19</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>246</v>
+        <v>225</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
@@ -3343,7 +3327,7 @@
         <v>20</v>
       </c>
       <c r="C107" t="s">
-        <v>247</v>
+        <v>226</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -3354,7 +3338,7 @@
         <v>21</v>
       </c>
       <c r="C108" t="s">
-        <v>248</v>
+        <v>227</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
@@ -3365,7 +3349,7 @@
         <v>22</v>
       </c>
       <c r="C109" t="s">
-        <v>249</v>
+        <v>228</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
@@ -3376,7 +3360,7 @@
         <v>23</v>
       </c>
       <c r="C110" t="s">
-        <v>250</v>
+        <v>229</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
@@ -3387,7 +3371,7 @@
         <v>24</v>
       </c>
       <c r="C111" t="s">
-        <v>251</v>
+        <v>230</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
@@ -3398,7 +3382,7 @@
         <v>25</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>252</v>
+        <v>231</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
@@ -3409,7 +3393,7 @@
         <v>26</v>
       </c>
       <c r="C113" t="s">
-        <v>253</v>
+        <v>232</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -3420,7 +3404,7 @@
         <v>27</v>
       </c>
       <c r="C114" t="s">
-        <v>254</v>
+        <v>233</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
@@ -3431,7 +3415,7 @@
         <v>28</v>
       </c>
       <c r="C115" t="s">
-        <v>255</v>
+        <v>234</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
@@ -3442,7 +3426,7 @@
         <v>29</v>
       </c>
       <c r="C116" t="s">
-        <v>256</v>
+        <v>235</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
@@ -3453,7 +3437,7 @@
         <v>30</v>
       </c>
       <c r="C117" t="s">
-        <v>257</v>
+        <v>236</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
@@ -3464,7 +3448,7 @@
         <v>31</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>258</v>
+        <v>237</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
@@ -3475,7 +3459,7 @@
         <v>32</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>238</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
@@ -3486,7 +3470,7 @@
         <v>33</v>
       </c>
       <c r="C120" t="s">
-        <v>260</v>
+        <v>239</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
@@ -3497,7 +3481,7 @@
         <v>34</v>
       </c>
       <c r="C121" t="s">
-        <v>261</v>
+        <v>240</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
@@ -3508,7 +3492,7 @@
         <v>35</v>
       </c>
       <c r="C122" t="s">
-        <v>262</v>
+        <v>241</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
@@ -3519,7 +3503,7 @@
         <v>36</v>
       </c>
       <c r="C123" t="s">
-        <v>263</v>
+        <v>242</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
@@ -3530,7 +3514,7 @@
         <v>37</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>264</v>
+        <v>243</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
@@ -3541,7 +3525,7 @@
         <v>38</v>
       </c>
       <c r="C125" t="s">
-        <v>265</v>
+        <v>244</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
@@ -3552,7 +3536,7 @@
         <v>39</v>
       </c>
       <c r="C126" t="s">
-        <v>266</v>
+        <v>245</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
@@ -3563,7 +3547,7 @@
         <v>40</v>
       </c>
       <c r="C127" t="s">
-        <v>267</v>
+        <v>246</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
@@ -3574,7 +3558,7 @@
         <v>41</v>
       </c>
       <c r="C128" t="s">
-        <v>268</v>
+        <v>247</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
@@ -3585,7 +3569,7 @@
         <v>42</v>
       </c>
       <c r="C129" t="s">
-        <v>269</v>
+        <v>248</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
@@ -3596,7 +3580,7 @@
         <v>43</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>270</v>
+        <v>249</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
@@ -3607,7 +3591,7 @@
         <v>44</v>
       </c>
       <c r="C131" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
@@ -3618,7 +3602,7 @@
         <v>45</v>
       </c>
       <c r="C132" t="s">
-        <v>272</v>
+        <v>251</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
@@ -3629,7 +3613,7 @@
         <v>46</v>
       </c>
       <c r="C133" t="s">
-        <v>273</v>
+        <v>252</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
@@ -3640,7 +3624,7 @@
         <v>47</v>
       </c>
       <c r="C134" t="s">
-        <v>274</v>
+        <v>253</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
@@ -3651,7 +3635,7 @@
         <v>48</v>
       </c>
       <c r="C135" t="s">
-        <v>275</v>
+        <v>254</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
@@ -3662,7 +3646,7 @@
         <v>49</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>276</v>
+        <v>255</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
@@ -3673,7 +3657,7 @@
         <v>50</v>
       </c>
       <c r="C137" t="s">
-        <v>277</v>
+        <v>256</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
@@ -3684,7 +3668,7 @@
         <v>51</v>
       </c>
       <c r="C138" t="s">
-        <v>278</v>
+        <v>257</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
@@ -3695,7 +3679,7 @@
         <v>1</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>279</v>
+        <v>258</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
@@ -3706,7 +3690,7 @@
         <v>2</v>
       </c>
       <c r="C140" t="s">
-        <v>280</v>
+        <v>259</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
@@ -3717,7 +3701,7 @@
         <v>3</v>
       </c>
       <c r="C141" t="s">
-        <v>281</v>
+        <v>260</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
@@ -3728,7 +3712,7 @@
         <v>4</v>
       </c>
       <c r="C142" t="s">
-        <v>282</v>
+        <v>261</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
@@ -3739,7 +3723,7 @@
         <v>1</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>283</v>
+        <v>262</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
@@ -3750,7 +3734,7 @@
         <v>2</v>
       </c>
       <c r="C144" t="s">
-        <v>284</v>
+        <v>263</v>
       </c>
     </row>
     <row r="145" spans="1:30" x14ac:dyDescent="0.25">
@@ -3761,7 +3745,7 @@
         <v>3</v>
       </c>
       <c r="C145" t="s">
-        <v>285</v>
+        <v>264</v>
       </c>
     </row>
     <row r="146" spans="1:30" x14ac:dyDescent="0.25">
@@ -3772,7 +3756,7 @@
         <v>4</v>
       </c>
       <c r="C146" t="s">
-        <v>286</v>
+        <v>265</v>
       </c>
     </row>
     <row r="147" spans="1:30" x14ac:dyDescent="0.25">
@@ -3783,7 +3767,7 @@
         <v>1</v>
       </c>
       <c r="C147" t="s">
-        <v>287</v>
+        <v>266</v>
       </c>
       <c r="F147" s="1"/>
       <c r="L147" s="1"/>
@@ -3799,7 +3783,7 @@
         <v>2</v>
       </c>
       <c r="C148" t="s">
-        <v>288</v>
+        <v>267</v>
       </c>
       <c r="F148" s="1"/>
       <c r="L148" s="1"/>
@@ -3811,154 +3795,154 @@
       <c r="A149" t="s">
         <v>41</v>
       </c>
-      <c r="B149" s="2">
+      <c r="B149">
         <v>1</v>
       </c>
       <c r="C149" t="s">
-        <v>303</v>
+        <v>282</v>
       </c>
     </row>
     <row r="150" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>41</v>
       </c>
-      <c r="B150" s="2">
+      <c r="B150">
         <v>2</v>
       </c>
       <c r="C150" t="s">
-        <v>304</v>
+        <v>283</v>
       </c>
     </row>
     <row r="151" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>41</v>
       </c>
-      <c r="B151" s="2">
+      <c r="B151">
         <v>3</v>
       </c>
       <c r="C151" t="s">
-        <v>305</v>
+        <v>284</v>
       </c>
     </row>
     <row r="152" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>41</v>
       </c>
-      <c r="B152" s="2">
+      <c r="B152">
         <v>4</v>
       </c>
       <c r="C152" t="s">
-        <v>306</v>
+        <v>285</v>
       </c>
     </row>
     <row r="153" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>41</v>
       </c>
-      <c r="B153" s="2">
+      <c r="B153">
         <v>5</v>
       </c>
       <c r="C153" t="s">
-        <v>307</v>
+        <v>286</v>
       </c>
     </row>
     <row r="154" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>41</v>
       </c>
-      <c r="B154" s="2">
+      <c r="B154">
         <v>6</v>
       </c>
       <c r="C154" t="s">
-        <v>308</v>
+        <v>287</v>
       </c>
     </row>
     <row r="155" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>41</v>
       </c>
-      <c r="B155" s="2">
+      <c r="B155">
         <v>7</v>
       </c>
       <c r="C155" t="s">
-        <v>309</v>
+        <v>288</v>
       </c>
     </row>
     <row r="156" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>41</v>
       </c>
-      <c r="B156" s="2">
+      <c r="B156">
         <v>8</v>
       </c>
       <c r="C156" t="s">
-        <v>310</v>
+        <v>289</v>
       </c>
     </row>
     <row r="157" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>41</v>
       </c>
-      <c r="B157" s="2">
+      <c r="B157">
         <v>9</v>
       </c>
       <c r="C157" t="s">
-        <v>311</v>
+        <v>290</v>
       </c>
     </row>
     <row r="158" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>41</v>
       </c>
-      <c r="B158" s="2">
+      <c r="B158">
         <v>10</v>
       </c>
       <c r="C158" t="s">
-        <v>312</v>
+        <v>291</v>
       </c>
     </row>
     <row r="159" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>41</v>
       </c>
-      <c r="B159" s="2">
+      <c r="B159">
         <v>11</v>
       </c>
       <c r="C159" t="s">
-        <v>313</v>
+        <v>292</v>
       </c>
     </row>
     <row r="160" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>41</v>
       </c>
-      <c r="B160" s="2">
+      <c r="B160">
         <v>12</v>
       </c>
       <c r="C160" t="s">
-        <v>314</v>
+        <v>293</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>41</v>
       </c>
-      <c r="B161" s="2">
+      <c r="B161">
         <v>13</v>
       </c>
       <c r="C161" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>41</v>
       </c>
-      <c r="B162" s="2">
+      <c r="B162">
         <v>14</v>
       </c>
       <c r="C162" t="s">
-        <v>316</v>
+        <v>295</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
@@ -3969,7 +3953,7 @@
         <v>1</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>289</v>
+        <v>268</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
@@ -3980,7 +3964,7 @@
         <v>2</v>
       </c>
       <c r="C164" t="s">
-        <v>291</v>
+        <v>270</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
@@ -3991,7 +3975,7 @@
         <v>3</v>
       </c>
       <c r="C165" t="s">
-        <v>292</v>
+        <v>271</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
@@ -4002,249 +3986,249 @@
         <v>4</v>
       </c>
       <c r="C166" t="s">
-        <v>290</v>
+        <v>269</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>164</v>
+        <v>143</v>
       </c>
       <c r="B167">
         <v>0</v>
       </c>
       <c r="C167" t="s">
-        <v>214</v>
+        <v>193</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>164</v>
+        <v>143</v>
       </c>
       <c r="B168">
         <v>1</v>
       </c>
       <c r="C168" t="s">
-        <v>215</v>
+        <v>194</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="B169">
         <v>0</v>
       </c>
       <c r="C169" t="s">
-        <v>214</v>
+        <v>193</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="B170">
         <v>1</v>
       </c>
       <c r="C170" t="s">
-        <v>215</v>
+        <v>194</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>166</v>
+        <v>145</v>
       </c>
       <c r="B171">
         <v>0</v>
       </c>
       <c r="C171" t="s">
-        <v>214</v>
+        <v>193</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>166</v>
+        <v>145</v>
       </c>
       <c r="B172">
         <v>1</v>
       </c>
       <c r="C172" t="s">
-        <v>215</v>
+        <v>194</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="B173">
         <v>0</v>
       </c>
       <c r="C173" t="s">
-        <v>214</v>
+        <v>193</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="B174">
         <v>1</v>
       </c>
       <c r="C174" t="s">
-        <v>215</v>
+        <v>194</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>168</v>
+        <v>147</v>
       </c>
       <c r="B175">
         <v>0</v>
       </c>
       <c r="C175" t="s">
-        <v>214</v>
+        <v>193</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>168</v>
+        <v>147</v>
       </c>
       <c r="B176">
         <v>1</v>
       </c>
       <c r="C176" t="s">
-        <v>215</v>
+        <v>194</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>169</v>
+        <v>148</v>
       </c>
       <c r="B177">
         <v>0</v>
       </c>
       <c r="C177" t="s">
-        <v>214</v>
+        <v>193</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>169</v>
+        <v>148</v>
       </c>
       <c r="B178">
         <v>1</v>
       </c>
       <c r="C178" t="s">
-        <v>215</v>
+        <v>194</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>170</v>
+        <v>149</v>
       </c>
       <c r="B179">
         <v>0</v>
       </c>
       <c r="C179" t="s">
-        <v>214</v>
+        <v>193</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>170</v>
+        <v>149</v>
       </c>
       <c r="B180">
         <v>1</v>
       </c>
       <c r="C180" t="s">
-        <v>215</v>
+        <v>194</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>171</v>
+        <v>150</v>
       </c>
       <c r="B181">
         <v>0</v>
       </c>
       <c r="C181" t="s">
-        <v>214</v>
+        <v>193</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>171</v>
+        <v>150</v>
       </c>
       <c r="B182">
         <v>1</v>
       </c>
       <c r="C182" t="s">
-        <v>215</v>
+        <v>194</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>172</v>
+        <v>151</v>
       </c>
       <c r="B183">
         <v>0</v>
       </c>
       <c r="C183" t="s">
-        <v>214</v>
+        <v>193</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>172</v>
+        <v>151</v>
       </c>
       <c r="B184">
         <v>1</v>
       </c>
       <c r="C184" t="s">
-        <v>215</v>
+        <v>194</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>173</v>
+        <v>152</v>
       </c>
       <c r="B185">
         <v>0</v>
       </c>
       <c r="C185" t="s">
-        <v>214</v>
+        <v>193</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>173</v>
+        <v>152</v>
       </c>
       <c r="B186">
         <v>1</v>
       </c>
       <c r="C186" t="s">
-        <v>215</v>
+        <v>194</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>175</v>
+        <v>154</v>
       </c>
       <c r="B187">
         <v>0</v>
       </c>
       <c r="C187" t="s">
-        <v>328</v>
+        <v>307</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>175</v>
+        <v>154</v>
       </c>
       <c r="B188">
         <v>1</v>
       </c>
       <c r="C188" t="s">
-        <v>203</v>
+        <v>182</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
@@ -4255,7 +4239,7 @@
         <v>0</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>294</v>
+        <v>273</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
@@ -4266,7 +4250,7 @@
         <v>1</v>
       </c>
       <c r="C190" t="s">
-        <v>295</v>
+        <v>274</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
@@ -4277,7 +4261,7 @@
         <v>2</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>296</v>
+        <v>275</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
@@ -4288,7 +4272,7 @@
         <v>3</v>
       </c>
       <c r="C192" t="s">
-        <v>297</v>
+        <v>276</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
@@ -4299,7 +4283,7 @@
         <v>4</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>298</v>
+        <v>277</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
@@ -4310,7 +4294,7 @@
         <v>5</v>
       </c>
       <c r="C194" t="s">
-        <v>299</v>
+        <v>278</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
@@ -4321,7 +4305,7 @@
         <v>6</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>300</v>
+        <v>279</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
@@ -4332,7 +4316,7 @@
         <v>7</v>
       </c>
       <c r="C196" t="s">
-        <v>302</v>
+        <v>281</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
@@ -4343,62 +4327,62 @@
         <v>8</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>301</v>
+        <v>280</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>55</v>
       </c>
-      <c r="B198" s="2">
+      <c r="B198">
         <v>-99</v>
       </c>
       <c r="C198" t="s">
-        <v>203</v>
+        <v>182</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>55</v>
       </c>
-      <c r="B199" s="2">
+      <c r="B199">
         <v>-98</v>
       </c>
       <c r="C199" t="s">
-        <v>317</v>
+        <v>296</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>55</v>
       </c>
-      <c r="B200" s="2">
+      <c r="B200">
         <v>0</v>
       </c>
       <c r="C200" t="s">
-        <v>318</v>
+        <v>297</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>55</v>
       </c>
-      <c r="B201" s="2">
+      <c r="B201">
         <v>1</v>
       </c>
       <c r="C201" t="s">
-        <v>319</v>
+        <v>298</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>55</v>
       </c>
-      <c r="B202" s="2">
+      <c r="B202">
         <v>2</v>
       </c>
       <c r="C202" t="s">
-        <v>320</v>
+        <v>299</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
@@ -4409,7 +4393,7 @@
         <v>-99</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>203</v>
+        <v>182</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -4420,7 +4404,7 @@
         <v>-98</v>
       </c>
       <c r="C204" t="s">
-        <v>221</v>
+        <v>200</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
@@ -4431,7 +4415,7 @@
         <v>1</v>
       </c>
       <c r="C205" t="s">
-        <v>321</v>
+        <v>300</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
@@ -4442,7 +4426,7 @@
         <v>2</v>
       </c>
       <c r="C206" t="s">
-        <v>322</v>
+        <v>301</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
@@ -4453,7 +4437,7 @@
         <v>3</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>323</v>
+        <v>302</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -4464,7 +4448,7 @@
         <v>4</v>
       </c>
       <c r="C208" t="s">
-        <v>324</v>
+        <v>303</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
@@ -4475,18 +4459,18 @@
         <v>5</v>
       </c>
       <c r="C209" t="s">
-        <v>325</v>
+        <v>304</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>57</v>
       </c>
-      <c r="B210" s="2">
+      <c r="B210">
         <v>0</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>326</v>
+        <v>305</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
@@ -4497,7 +4481,7 @@
         <v>1</v>
       </c>
       <c r="C211" t="s">
-        <v>327</v>
+        <v>306</v>
       </c>
     </row>
   </sheetData>
